--- a/PPG/Coordenação.xlsx
+++ b/PPG/Coordenação.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurdesaferreira1/Documents/Google drive (arthur_sf)/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D285D62-EE65-BD48-857D-6AB2E732750E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A22D03E-D987-DD40-8541-A460DB13AD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="500" windowWidth="27880" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="660" windowWidth="27880" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordenação" sheetId="17" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>Nome</t>
   </si>
@@ -136,6 +136,12 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1-LiUfjJ3tU2NoUOj9GFaFMt59DkXyKf4</t>
+  </si>
+  <si>
+    <t>Luis Felipe Fonseca Reis</t>
+  </si>
+  <si>
+    <t>luisfelipefreis@souunisuam.com.br</t>
   </si>
 </sst>
 </file>
@@ -548,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787254B8-2D79-7240-B890-7E7B72FB03AB}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" style="4" bestFit="1" customWidth="1"/>
@@ -623,6 +629,9 @@
       <c r="D4" s="5">
         <v>42387</v>
       </c>
+      <c r="E4" s="5">
+        <v>45447</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
@@ -637,9 +646,26 @@
       <c r="D5" s="5">
         <v>42387</v>
       </c>
+      <c r="E5" s="5">
+        <v>45447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="5">
+        <v>45447</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
+  <conditionalFormatting sqref="E1:E3 E6:E1048576">
     <cfRule type="containsText" dxfId="0" priority="29" operator="containsText" text="Atual">
       <formula>NOT(ISERROR(SEARCH("Atual",E1)))</formula>
     </cfRule>
